--- a/auto OMS Python/engines/shopee/basic_chihuy1984.xlsx
+++ b/auto OMS Python/engines/shopee/basic_chihuy1984.xlsx
@@ -416,6 +416,43 @@
 #tacke #tackenhua #shophuyvan</t>
   </si>
   <si>
+    <t>14815890188</t>
+  </si>
+  <si>
+    <t>Kẹp Cố Định Dây Điện, Cáp Mạng K114 – Keo Nano Siêu Dính, Không Cần Khoan</t>
+  </si>
+  <si>
+    <t>Bạn đang đau đầu vì dây điện, cáp sạc, dây mạng loằng ngoằng khắp nhà hay nơi làm việc?
+👉 Hãy sử dụng Kẹp cố định dây điện/cáp mạng K114, giải pháp gọn nhẹ giúp giữ dây ngăn nắp – không cần khoan đục – không để lại vết keo!
+✅ ƯU ĐIỂM NỔI BẬT:
+Keo nano siêu dính, bám chắc trên nhiều bề mặt như tường, gỗ, kính, nhựa, kim loại…
+Không cần khoan hay bắt vít, dễ lắp – dễ tháo – không để lại dấu vết.
+Giữ không gian sạch sẽ, ngăn nắp – không còn cảnh dây dợ lộn xộn khắp nơi.
+Tùy chọn nhiều kích thước: Phù hợp với dây tai nghe, dây sạc, dây mạng, cáp máy tính, dây nguồn TV, máy in...
+Thiết kế nhỏ gọn, màu đen/trắng tinh tế, không ảnh hưởng đến thẩm mỹ không gian.
+Dùng được cho gia đình, văn phòng, xe hơi…
+📦 THÔNG TIN SẢN PHẨM:
+🔹 Phân loại 12MM:
+– Chất liệu: Nhựa
+– Bán kính: 12mm
+– Màu: Trắng hoặc Đen
+– Phù hợp: Cáp nhỏ, dây sạc điện thoại, tai nghe, cáp USB…
+🔹 Phân loại 16MM:
+– Kích thước: 40x30x20mm
+– Bán kính: 16mm
+– Phù hợp: Dây mạng, dây điện gia dụng, dây máy tính
+🔹 Phân loại 22MM:
+– Kích thước: 43x45x25mm
+– Bán kính: 22mm
+– Phù hợp: Dây điện lớn, dây nguồn máy lạnh, máy giặt...
+📍 Xuất xứ: Trung Quốc
+🛠 HƯỚNG DẪN SỬ DỤNG:
+Lau sạch bề mặt cần dán.
+Bóc lớp keo phía sau kẹp và dán lên vị trí mong muốn.
+Cố định dây vào kẹp.
+👉 Dễ dàng gỡ ra khi cần thay đổi vị trí, không để lại vết keo!</t>
+  </si>
+  <si>
     <t>12455764340</t>
   </si>
   <si>
@@ -451,43 +488,6 @@
  ★ Luôn Kiểm Tra Kỹ Hàng Hoá Trước Khi Giao Cho Khách.
  ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
  ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!</t>
-  </si>
-  <si>
-    <t>14815890188</t>
-  </si>
-  <si>
-    <t>Kẹp Cố Định Dây Điện, Cáp Mạng K114 – Keo Nano Siêu Dính, Không Cần Khoan</t>
-  </si>
-  <si>
-    <t>Bạn đang đau đầu vì dây điện, cáp sạc, dây mạng loằng ngoằng khắp nhà hay nơi làm việc?
-👉 Hãy sử dụng Kẹp cố định dây điện/cáp mạng K114, giải pháp gọn nhẹ giúp giữ dây ngăn nắp – không cần khoan đục – không để lại vết keo!
-✅ ƯU ĐIỂM NỔI BẬT:
-Keo nano siêu dính, bám chắc trên nhiều bề mặt như tường, gỗ, kính, nhựa, kim loại…
-Không cần khoan hay bắt vít, dễ lắp – dễ tháo – không để lại dấu vết.
-Giữ không gian sạch sẽ, ngăn nắp – không còn cảnh dây dợ lộn xộn khắp nơi.
-Tùy chọn nhiều kích thước: Phù hợp với dây tai nghe, dây sạc, dây mạng, cáp máy tính, dây nguồn TV, máy in...
-Thiết kế nhỏ gọn, màu đen/trắng tinh tế, không ảnh hưởng đến thẩm mỹ không gian.
-Dùng được cho gia đình, văn phòng, xe hơi…
-📦 THÔNG TIN SẢN PHẨM:
-🔹 Phân loại 12MM:
-– Chất liệu: Nhựa
-– Bán kính: 12mm
-– Màu: Trắng hoặc Đen
-– Phù hợp: Cáp nhỏ, dây sạc điện thoại, tai nghe, cáp USB…
-🔹 Phân loại 16MM:
-– Kích thước: 40x30x20mm
-– Bán kính: 16mm
-– Phù hợp: Dây mạng, dây điện gia dụng, dây máy tính
-🔹 Phân loại 22MM:
-– Kích thước: 43x45x25mm
-– Bán kính: 22mm
-– Phù hợp: Dây điện lớn, dây nguồn máy lạnh, máy giặt...
-📍 Xuất xứ: Trung Quốc
-🛠 HƯỚNG DẪN SỬ DỤNG:
-Lau sạch bề mặt cần dán.
-Bóc lớp keo phía sau kẹp và dán lên vị trí mong muốn.
-Cố định dây vào kẹp.
-👉 Dễ dàng gỡ ra khi cần thay đổi vị trí, không để lại vết keo!</t>
   </si>
   <si>
     <t>24418368117</t>
@@ -997,6 +997,26 @@
 #mutambe #mutam</t>
   </si>
   <si>
+    <t>24768421006</t>
+  </si>
+  <si>
+    <t>COMBO 20 Tắc Kê Sắt + 20 Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
+  </si>
+  <si>
+    <t>Cung cấp đa dạng các combo tắc kê sắt đuôi cá kèm vít chất lượng, đáp ứng mọi nhu cầu lắp đặt từ tải trọng nhẹ đến tải trọng nặng.
+Sản phẩm làm từ thép mạ kẽm, chống rỉ sét, đảm bảo độ bám chắc chắn và an toàn tuyệt đối khi lắp đặt trên các loại vật liệu xây dựng như gạch, bê tông, đá.
+Thông Tin Sản Phẩm :
+- Tên Sản Phẩm : Tắc Kê Sắt
+- Có 3 Kích Thước Xem Hình ở Phân Loại Để Mua Đúng Kích Thước mình cần
+  Phân Loại 1 : 20 tắc kê 5mm*30mm + 20 vít 4mm*30mm (Khoan Lỗ 6MM)
+  Phân Loại 2 : 20 tắc kê 6mm*32mm + 20 vít 5mm*40mm (Khoan Lỗ 8MM)
+  Phân Loại 3 : 20 tắc kê 8mm*60mm + 20 vít 6mm*60mm (Khoan Lỗ 10MM)
+- Chất Liệu Được Làm Bằng Sắt 
+Sử Dụng Đơn giản như tắc kê nhựa nhưng độ chịu lực thì gấp nhiều lần tắc kê nhựa ạ
+#tacke #tackenhua #shophuyvan
+</t>
+  </si>
+  <si>
     <t>5948362499</t>
   </si>
   <si>
@@ -1096,6 +1116,30 @@
  ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
  ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!
 #tuirac, #túirác, #tuiracgiare, #túirácgiárẻ, #túiráccuộn, #tuiraccuon, #tuidungrac, #túiđựngrác, #thungrac</t>
+  </si>
+  <si>
+    <t>13615381825</t>
+  </si>
+  <si>
+    <t>Bộ 100 Đinh 2 Đầu Dùng Để Đóng Chân Tường ,Tủ Kệ Bếp Che Khuyết Điểm K97</t>
+  </si>
+  <si>
+    <t>
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz913rcadh9d55
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz913rkm1aqp77
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz913s3h9oi506
+ - Xuất Xứ : Trung Quốc
+ - Sản Phẩm Được Nhập Và Phân Phối Bởi Kho Gia Dụng Huy Vân
+ - .
+ Dịch vụ tốt nhất:
+ ★ Cam Kết Sản Phẩm Và Chất Lượng Như Hình Và Video Shop Đăng,Tuyệt Đối Không Bán Hàng Kém Chất Lượng ảnh hưởng đến UY TÍN Của Shop
+ ★ Ship Hoả Tốc Trong Vòng 2H Kể Từ Khi Khách Đặt Hàng (Xác Nhận Đơn Đến 19-20H Hàng Ngày)
+ ★ Cam Kết Giao Đơn Hàng Cho Đơn Vị Vận Chuyển Trong Vòng 24H Kể Từ Khi Qúi Khách Đặt Hàng
+ ★ Hàng Hoá Luôn Có Sẵn Khách Đặt Được Là Còn Hàng ( Nếu Hết Hàng Shop Sẽ Gọi Điện Liên Hệ Khách Trước Khi Giao)
+ ★ Luôn Kiểm Tra Kỹ Hàng Hoá Trước Khi Giao Cho Khách.
+ ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
+ ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!
+#dinh2dau #dinh2daunhon #dinhdongtu #dinhdongchantuong #shophuyvan</t>
   </si>
   <si>
     <t>6856001620</t>
@@ -1244,30 +1288,6 @@
  ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!</t>
   </si>
   <si>
-    <t>13615381825</t>
-  </si>
-  <si>
-    <t>Bộ 100 Đinh 2 Đầu Dùng Để Đóng Chân Tường ,Tủ Kệ Bếp Che Khuyết Điểm K97</t>
-  </si>
-  <si>
-    <t>
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz913rcadh9d55
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz913rkm1aqp77
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz913s3h9oi506
- - Xuất Xứ : Trung Quốc
- - Sản Phẩm Được Nhập Và Phân Phối Bởi Kho Gia Dụng Huy Vân
- - .
- Dịch vụ tốt nhất:
- ★ Cam Kết Sản Phẩm Và Chất Lượng Như Hình Và Video Shop Đăng,Tuyệt Đối Không Bán Hàng Kém Chất Lượng ảnh hưởng đến UY TÍN Của Shop
- ★ Ship Hoả Tốc Trong Vòng 2H Kể Từ Khi Khách Đặt Hàng (Xác Nhận Đơn Đến 19-20H Hàng Ngày)
- ★ Cam Kết Giao Đơn Hàng Cho Đơn Vị Vận Chuyển Trong Vòng 24H Kể Từ Khi Qúi Khách Đặt Hàng
- ★ Hàng Hoá Luôn Có Sẵn Khách Đặt Được Là Còn Hàng ( Nếu Hết Hàng Shop Sẽ Gọi Điện Liên Hệ Khách Trước Khi Giao)
- ★ Luôn Kiểm Tra Kỹ Hàng Hoá Trước Khi Giao Cho Khách.
- ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
- ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!
-#dinh2dau #dinh2daunhon #dinhdongtu #dinhdongchantuong #shophuyvan</t>
-  </si>
-  <si>
     <t>7756001691</t>
   </si>
   <si>
@@ -1383,26 +1403,6 @@
  ★ Luôn Kiểm Tra Kỹ Hàng Hoá Trước Khi Giao Cho Khách.
  ★ Bảo vệ khách hàng : Khi Nhận Được Sản Phẩm Bị Thiếu Hoặc Lỗi Do Phía Vận Chuyển Qúi Khách Vui Lòng Liên Hệ Lại Shop Để Shop xử lý Vấn Đề Ngay ạ
  ★ Qúi Khách có thể thấy rằng ai đó bán với giá thấp hơn chúng tôi nhưng họ không thể đảm bảo chất lượng và dịch vụ như chúng tôi, cảm ơn bạn!</t>
-  </si>
-  <si>
-    <t>24768421006</t>
-  </si>
-  <si>
-    <t>COMBO 20 Tắc Kê Sắt + 20 Vít Chịu Lực Cực Tốt Không Sợ Bung Và Rơi Rớt Mọi Vật Dụng Treo Tường Sau Khi Lắp Đặt K243</t>
-  </si>
-  <si>
-    <t>Cung cấp đa dạng các combo tắc kê sắt đuôi cá kèm vít chất lượng, đáp ứng mọi nhu cầu lắp đặt từ tải trọng nhẹ đến tải trọng nặng.
-Sản phẩm làm từ thép mạ kẽm, chống rỉ sét, đảm bảo độ bám chắc chắn và an toàn tuyệt đối khi lắp đặt trên các loại vật liệu xây dựng như gạch, bê tông, đá.
-Thông Tin Sản Phẩm :
-- Tên Sản Phẩm : Tắc Kê Sắt
-- Có 3 Kích Thước Xem Hình ở Phân Loại Để Mua Đúng Kích Thước mình cần
-  Phân Loại 1 : 20 tắc kê 5mm*30mm + 20 vít 4mm*30mm (Khoan Lỗ 6MM)
-  Phân Loại 2 : 20 tắc kê 6mm*32mm + 20 vít 5mm*40mm (Khoan Lỗ 8MM)
-  Phân Loại 3 : 20 tắc kê 8mm*60mm + 20 vít 6mm*60mm (Khoan Lỗ 10MM)
-- Chất Liệu Được Làm Bằng Sắt 
-Sử Dụng Đơn giản như tắc kê nhựa nhưng độ chịu lực thì gấp nhiều lần tắc kê nhựa ạ
-#tacke #tackenhua #shophuyvan
-</t>
   </si>
   <si>
     <t>9523434925</t>
@@ -2819,36 +2819,6 @@
 #mayhutchankhongquanaomini
 #mayhutchankhongcucmanh
 #mayhutchankhongquanaocucmanh</t>
-  </si>
-  <si>
-    <t>8088637510</t>
-  </si>
-  <si>
-    <t>Đầu Vòi Rửa Bát Tăng Áp K50 – Xoay 360 Độ, Lọc Nước, Lắp Siêu Dễ</t>
-  </si>
-  <si>
-    <t>💢 Xoay 360 độ, rửa mọi thứ, mọi ngóc ngách trong bồn rửa bát một cách tiện lợi, dễ dàng
-💢 giúp vòi nước cao không bị bắn tung tóe ạ, điều chỉnh dòng nước theo ý mình
-💢 Đầu Lọc Dễ Dàng Thay Thế Và Có Thể Sử Dụng Từ 1 -3 tháng Mới Phải Thay Đầu Lọc 1 Lần
-💢 Bộ Sản Phẩm Gồm : 1 Đầu Vòi Kèm Bộ Lọc + 2 Miếng Zon
-💢 Shop Có Bán Riêng Lõi Lọc Và Đầu Vạn Năng Để Lắp Được Hầu Hết Các Loại Vòi
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz9144n6wntt6c
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz9144tknbmp3e
-   Thông Tin Sản Phẩm
- - Chất Liệu : Nhựa ABS + Lõi Lọc Bằng Màng Lọc PP
- - Kích Thước :  7.5CM X 4CM
- - Xuất Xứ : Trung Quốc
- - Sản Phẩm Được Nhập Và Phân Phối Bởi Kho Gia Dụng Huy Vân
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz9145940kstad
-https://cf.shopee.vn/file/vn-11134202-7r98o-lz9145gbq0r1ae
- ★ Lưu ý: 
-  - Quý Khách Nên Mua Kèm Đầu Vạn Năng Để Có Thể Lắp Đặt Được Hầu Hết Các Loại Vòi ạ
-  - do chênh lệch ánh sáng và màn hình, màu sắc của sản phẩm có thể hơi khác so với hình ảnh.
-  - Vui Lòng Cho Phép Sai Số 1-2cm do đo lường thủ công
-#Đầuvòitắngáp
-#Đầuvòităngáplựcnước
-#Đầuvòităngápxoay360độ
-#Vòinốirửabáttăngáp</t>
   </si>
   <si>
     <t>13840948033</t>
@@ -2907,6 +2877,36 @@
 #tuilocracbonruachen
 #locracbonruabat
 #khaylocracbonruabat</t>
+  </si>
+  <si>
+    <t>8088637510</t>
+  </si>
+  <si>
+    <t>Đầu Vòi Rửa Bát Tăng Áp K50 – Xoay 360 Độ, Lọc Nước, Lắp Siêu Dễ</t>
+  </si>
+  <si>
+    <t>💢 Xoay 360 độ, rửa mọi thứ, mọi ngóc ngách trong bồn rửa bát một cách tiện lợi, dễ dàng
+💢 giúp vòi nước cao không bị bắn tung tóe ạ, điều chỉnh dòng nước theo ý mình
+💢 Đầu Lọc Dễ Dàng Thay Thế Và Có Thể Sử Dụng Từ 1 -3 tháng Mới Phải Thay Đầu Lọc 1 Lần
+💢 Bộ Sản Phẩm Gồm : 1 Đầu Vòi Kèm Bộ Lọc + 2 Miếng Zon
+💢 Shop Có Bán Riêng Lõi Lọc Và Đầu Vạn Năng Để Lắp Được Hầu Hết Các Loại Vòi
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz9144n6wntt6c
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz9144tknbmp3e
+   Thông Tin Sản Phẩm
+ - Chất Liệu : Nhựa ABS + Lõi Lọc Bằng Màng Lọc PP
+ - Kích Thước :  7.5CM X 4CM
+ - Xuất Xứ : Trung Quốc
+ - Sản Phẩm Được Nhập Và Phân Phối Bởi Kho Gia Dụng Huy Vân
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz9145940kstad
+https://cf.shopee.vn/file/vn-11134202-7r98o-lz9145gbq0r1ae
+ ★ Lưu ý: 
+  - Quý Khách Nên Mua Kèm Đầu Vạn Năng Để Có Thể Lắp Đặt Được Hầu Hết Các Loại Vòi ạ
+  - do chênh lệch ánh sáng và màn hình, màu sắc của sản phẩm có thể hơi khác so với hình ảnh.
+  - Vui Lòng Cho Phép Sai Số 1-2cm do đo lường thủ công
+#Đầuvòitắngáp
+#Đầuvòităngáplựcnước
+#Đầuvòităngápxoay360độ
+#Vòinốirửabáttăngáp</t>
   </si>
   <si>
     <t>12460878593</t>
@@ -4576,153 +4576,153 @@
       <c r="A34" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="E34" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="35">
       <c r="A35" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="E35" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="36">
       <c r="A36" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="C36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="E36" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="37">
       <c r="A37" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="E37" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="38">
       <c r="A38" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="E38" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="39">
       <c r="A39" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="E39" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="40">
       <c r="A40" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E40" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="41">
       <c r="A41" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="E41" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="42">
       <c r="A42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E42" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="43">
       <c r="A43" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="E43" s="3"/>
     </row>
     <row customHeight="true" ht="15" r="44">
       <c r="A44" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B44" s="2"/>
       <c r="C44" s="2" t="s">
         <v>149</v>
       </c>
